--- a/Electronics & Compute part list_CN.xlsx
+++ b/Electronics & Compute part list_CN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\showcase\手搓智驾1_底盘\Aluminum-profile-go-kart-v2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E368B5E2-AB41-40ED-B46F-4E4C0DC28B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDDFD03C-787F-4E05-86BE-1FFB85D579D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$K$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$K$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="52">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -234,6 +234,18 @@
   </si>
   <si>
     <t>智能驾驶物料清单</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>双路刹车盒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>套</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>待添加链接</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -241,7 +253,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -297,6 +309,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -397,7 +416,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -432,6 +451,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -453,20 +484,11 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -624,13 +646,13 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>371476</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>57151</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>1304926</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>814057</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -668,13 +690,13 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>44672</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>1266280</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>856831</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -712,13 +734,13 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>390525</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>82164</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>1447093</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>790100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1065,7 +1087,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:L15"/>
+  <dimension ref="A2:L16"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.5" customWidth="1"/>
@@ -1081,41 +1103,41 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" ht="46.9" customHeight="1">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
       <c r="L2" s="10"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="25.15" customHeight="1">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="18">
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="22">
         <v>46097</v>
       </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="17" t="s">
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="15" t="s">
+      <c r="I3" s="21"/>
+      <c r="J3" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="16"/>
+      <c r="K3" s="20"/>
     </row>
     <row r="4" spans="1:12" s="1" customFormat="1" ht="22.15" customHeight="1">
       <c r="A4" s="3" t="s">
@@ -1154,8 +1176,11 @@
       <c r="L4" s="11"/>
     </row>
     <row r="5" spans="1:12" ht="66.75" customHeight="1">
+      <c r="A5" s="7">
+        <v>1</v>
+      </c>
       <c r="B5" s="4"/>
-      <c r="C5" s="19"/>
+      <c r="C5" s="12"/>
       <c r="D5" s="4" t="s">
         <v>16</v>
       </c>
@@ -1169,7 +1194,7 @@
       <c r="H5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="22" t="s">
+      <c r="I5" s="14" t="s">
         <v>22</v>
       </c>
       <c r="J5" s="4"/>
@@ -1178,31 +1203,34 @@
     </row>
     <row r="6" spans="1:12" ht="66.75" customHeight="1">
       <c r="A6" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="4"/>
-      <c r="C6" s="20"/>
+      <c r="C6" s="13"/>
       <c r="D6" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="21"/>
+      <c r="F6" s="4"/>
       <c r="G6" s="4">
         <v>1</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="22"/>
+      <c r="I6" s="14"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="L6" s="7"/>
     </row>
     <row r="7" spans="1:12" ht="66.75" customHeight="1">
+      <c r="A7" s="7">
+        <v>3</v>
+      </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="20"/>
+      <c r="C7" s="13"/>
       <c r="D7" s="4" t="s">
         <v>20</v>
       </c>
@@ -1216,26 +1244,26 @@
       <c r="H7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I7" s="22"/>
+      <c r="I7" s="14"/>
       <c r="J7" s="4"/>
-      <c r="K7" s="23" t="s">
+      <c r="K7" s="15" t="s">
         <v>47</v>
       </c>
       <c r="L7" s="7"/>
     </row>
     <row r="8" spans="1:12" ht="66.75" customHeight="1">
       <c r="A8" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B8" s="4"/>
-      <c r="C8" s="20"/>
+      <c r="C8" s="13"/>
       <c r="D8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="4" t="s">
         <v>25</v>
       </c>
       <c r="G8" s="4">
@@ -1244,26 +1272,28 @@
       <c r="H8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I8" s="22" t="s">
+      <c r="I8" s="14" t="s">
         <v>35</v>
       </c>
       <c r="J8" s="4"/>
-      <c r="K8" s="23" t="s">
+      <c r="K8" s="15" t="s">
         <v>46</v>
       </c>
       <c r="L8" s="7"/>
     </row>
     <row r="9" spans="1:12" ht="66.75" customHeight="1">
-      <c r="A9" s="4"/>
+      <c r="A9" s="7">
+        <v>5</v>
+      </c>
       <c r="B9" s="4"/>
-      <c r="C9" s="20"/>
+      <c r="C9" s="13"/>
       <c r="D9" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="F9" s="4" t="s">
         <v>29</v>
       </c>
       <c r="G9" s="4">
@@ -1272,7 +1302,7 @@
       <c r="H9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I9" s="22" t="s">
+      <c r="I9" s="14" t="s">
         <v>45</v>
       </c>
       <c r="J9" s="4"/>
@@ -1281,17 +1311,17 @@
     </row>
     <row r="10" spans="1:12" ht="66.75" customHeight="1">
       <c r="A10" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B10" s="4"/>
-      <c r="C10" s="20"/>
+      <c r="C10" s="13"/>
       <c r="D10" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="F10" s="4" t="s">
         <v>32</v>
       </c>
       <c r="G10" s="4">
@@ -1300,49 +1330,51 @@
       <c r="H10" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I10" s="22" t="s">
+      <c r="I10" s="14" t="s">
         <v>33</v>
       </c>
       <c r="J10" s="4"/>
-      <c r="K10" s="23" t="s">
+      <c r="K10" s="15" t="s">
         <v>44</v>
       </c>
       <c r="L10" s="7"/>
     </row>
     <row r="11" spans="1:12" ht="66.75" customHeight="1">
-      <c r="A11" s="4">
-        <v>4</v>
+      <c r="A11" s="7">
+        <v>7</v>
       </c>
       <c r="B11" s="4"/>
-      <c r="C11" s="20"/>
+      <c r="C11" s="13"/>
       <c r="D11" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" s="21"/>
+        <v>49</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
       <c r="G11" s="4">
         <v>1</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I11" s="22"/>
+        <v>50</v>
+      </c>
+      <c r="I11" s="24" t="s">
+        <v>51</v>
+      </c>
       <c r="J11" s="4"/>
-      <c r="K11" s="5"/>
+      <c r="K11" s="15"/>
       <c r="L11" s="7"/>
     </row>
     <row r="12" spans="1:12" ht="66.75" customHeight="1">
       <c r="A12" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B12" s="4"/>
-      <c r="C12" s="20"/>
+      <c r="C12" s="13"/>
       <c r="D12" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4">
         <v>1</v>
@@ -1350,23 +1382,19 @@
       <c r="H12" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="22" t="s">
-        <v>40</v>
-      </c>
+      <c r="I12" s="14"/>
       <c r="J12" s="4"/>
-      <c r="K12" s="23" t="s">
-        <v>43</v>
-      </c>
+      <c r="K12" s="5"/>
       <c r="L12" s="7"/>
     </row>
-    <row r="13" spans="1:12" ht="77.25" customHeight="1">
-      <c r="A13" s="4">
-        <v>6</v>
+    <row r="13" spans="1:12" ht="66.75" customHeight="1">
+      <c r="A13" s="7">
+        <v>9</v>
       </c>
       <c r="B13" s="4"/>
-      <c r="C13" s="20"/>
+      <c r="C13" s="13"/>
       <c r="D13" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
@@ -1376,48 +1404,74 @@
       <c r="H13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I13" s="22" t="s">
-        <v>41</v>
+      <c r="I13" s="14" t="s">
+        <v>40</v>
       </c>
       <c r="J13" s="4"/>
-      <c r="K13" s="23" t="s">
-        <v>42</v>
+      <c r="K13" s="15" t="s">
+        <v>43</v>
       </c>
       <c r="L13" s="7"/>
     </row>
-    <row r="14" spans="1:12" ht="55.9" customHeight="1">
-      <c r="A14" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="12"/>
+    <row r="14" spans="1:12" ht="77.25" customHeight="1">
+      <c r="A14" s="4">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4"/>
       <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="9"/>
+      <c r="D14" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="J14" s="4"/>
+      <c r="K14" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="L14" s="7"/>
     </row>
     <row r="15" spans="1:12" ht="55.9" customHeight="1">
-      <c r="A15" s="7"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
+      <c r="A15" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="16"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
       <c r="L15" s="9"/>
+    </row>
+    <row r="16" spans="1:12" ht="55.9" customHeight="1">
+      <c r="A16" s="7"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B14:K14"/>
+    <mergeCell ref="B15:K15"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="J3:K3"/>
     <mergeCell ref="H3:I3"/>
@@ -1426,14 +1480,14 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="K13" r:id="rId1" xr:uid="{4E0560E3-7655-4A48-A999-FB6EE3F46E84}"/>
-    <hyperlink ref="K12" r:id="rId2" xr:uid="{D43D9DFC-5391-466F-9020-80120B845907}"/>
+    <hyperlink ref="K14" r:id="rId1" xr:uid="{4E0560E3-7655-4A48-A999-FB6EE3F46E84}"/>
+    <hyperlink ref="K13" r:id="rId2" xr:uid="{D43D9DFC-5391-466F-9020-80120B845907}"/>
     <hyperlink ref="K10" r:id="rId3" xr:uid="{340DE177-23DD-4EBE-B763-488874B9DAB9}"/>
     <hyperlink ref="K8" r:id="rId4" xr:uid="{5101E1D1-455F-4BD8-BD65-70994219705D}"/>
     <hyperlink ref="K7" r:id="rId5" xr:uid="{382F4F4F-2BC6-40FB-BB7C-A95C73127A8F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.44" top="0.25" bottom="0.16" header="0.12" footer="0.09"/>
-  <pageSetup paperSize="9" scale="42" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId6"/>
+  <pageSetup paperSize="9" scale="44" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId6"/>
   <drawing r:id="rId7"/>
 </worksheet>
 </file>